--- a/GBDS MARCH FILES 2026/SCRR CALCULATOR - MARCH 2026.xlsx
+++ b/GBDS MARCH FILES 2026/SCRR CALCULATOR - MARCH 2026.xlsx
@@ -8,9 +8,9 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Users\User\Desktop\GBDS MARCH FILES 2026\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{441E92B5-DFDD-47A5-9667-503CCADFAB43}" xr6:coauthVersionLast="45" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{CE62F271-EA8C-4B03-86AF-747D6977ADEA}" xr6:coauthVersionLast="45" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
-    <workbookView xWindow="-120" yWindow="-120" windowWidth="29040" windowHeight="15840" activeTab="8" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
+    <workbookView xWindow="-120" yWindow="-120" windowWidth="29040" windowHeight="15840" firstSheet="7" activeTab="12" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
   <sheets>
     <sheet name="(March 2026)" sheetId="814" r:id="rId1"/>
@@ -89,7 +89,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="3770" uniqueCount="163">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="3778" uniqueCount="167">
   <si>
     <t>GUILLERMO BEVERAGE DISTRIBUTION SERVICES</t>
   </si>
@@ -702,6 +702,18 @@
       </rPr>
       <t xml:space="preserve">/ OVER </t>
     </r>
+  </si>
+  <si>
+    <t>52505</t>
+  </si>
+  <si>
+    <t>BALWARTE</t>
+  </si>
+  <si>
+    <t>147317</t>
+  </si>
+  <si>
+    <t>9125</t>
   </si>
 </sst>
 </file>
@@ -5781,10 +5793,12 @@
       <c r="B6" s="16" t="s">
         <v>15</v>
       </c>
-      <c r="C6" s="84"/>
+      <c r="C6" s="84">
+        <v>359</v>
+      </c>
       <c r="D6" s="13">
         <f t="shared" ref="D6:D28" si="1">C6*L6</f>
-        <v>0</v>
+        <v>273199</v>
       </c>
       <c r="F6" s="203" t="s">
         <v>16</v>
@@ -5817,10 +5831,12 @@
       <c r="B7" s="16" t="s">
         <v>18</v>
       </c>
-      <c r="C7" s="84"/>
+      <c r="C7" s="84">
+        <v>6</v>
+      </c>
       <c r="D7" s="13">
         <f t="shared" si="1"/>
-        <v>0</v>
+        <v>4686</v>
       </c>
       <c r="F7" s="204"/>
       <c r="G7" s="208"/>
@@ -5869,10 +5885,12 @@
       <c r="B9" s="16" t="s">
         <v>23</v>
       </c>
-      <c r="C9" s="84"/>
+      <c r="C9" s="84">
+        <v>117</v>
+      </c>
       <c r="D9" s="13">
         <f t="shared" si="1"/>
-        <v>0</v>
+        <v>85761</v>
       </c>
       <c r="F9" s="204"/>
       <c r="G9" s="215"/>
@@ -5893,10 +5911,12 @@
       <c r="B10" t="s">
         <v>25</v>
       </c>
-      <c r="C10" s="84"/>
+      <c r="C10" s="84">
+        <v>10</v>
+      </c>
       <c r="D10" s="13">
         <f t="shared" si="1"/>
-        <v>0</v>
+        <v>10320</v>
       </c>
       <c r="F10" s="203" t="s">
         <v>26</v>
@@ -5921,10 +5941,12 @@
       <c r="B11" s="17" t="s">
         <v>28</v>
       </c>
-      <c r="C11" s="84"/>
+      <c r="C11" s="84">
+        <v>2</v>
+      </c>
       <c r="D11" s="13">
         <f t="shared" si="1"/>
-        <v>0</v>
+        <v>2340</v>
       </c>
       <c r="F11" s="204"/>
       <c r="G11" s="215"/>
@@ -5953,10 +5975,12 @@
       <c r="B12" s="17" t="s">
         <v>30</v>
       </c>
-      <c r="C12" s="84"/>
+      <c r="C12" s="84">
+        <v>3</v>
+      </c>
       <c r="D12" s="48">
         <f t="shared" si="1"/>
-        <v>0</v>
+        <v>2976</v>
       </c>
       <c r="F12" s="221" t="s">
         <v>33</v>
@@ -5987,10 +6011,12 @@
       <c r="B13" s="17" t="s">
         <v>32</v>
       </c>
-      <c r="C13" s="84"/>
+      <c r="C13" s="84">
+        <v>18</v>
+      </c>
       <c r="D13" s="48">
         <f t="shared" si="1"/>
-        <v>0</v>
+        <v>5526</v>
       </c>
       <c r="F13" s="224" t="s">
         <v>36</v>
@@ -5998,7 +6024,7 @@
       <c r="G13" s="188"/>
       <c r="H13" s="179">
         <f>D29</f>
-        <v>0</v>
+        <v>387395</v>
       </c>
       <c r="I13" s="180"/>
       <c r="J13" s="181"/>
@@ -6021,10 +6047,12 @@
       <c r="B14" s="14" t="s">
         <v>35</v>
       </c>
-      <c r="C14" s="84"/>
+      <c r="C14" s="84">
+        <v>14</v>
+      </c>
       <c r="D14" s="31">
         <f t="shared" si="1"/>
-        <v>0</v>
+        <v>154</v>
       </c>
       <c r="F14" s="182" t="s">
         <v>39</v>
@@ -6032,7 +6060,7 @@
       <c r="G14" s="183"/>
       <c r="H14" s="184">
         <f>D54</f>
-        <v>0</v>
+        <v>43563.75</v>
       </c>
       <c r="I14" s="185"/>
       <c r="J14" s="186"/>
@@ -6070,7 +6098,7 @@
       <c r="G15" s="188"/>
       <c r="H15" s="189">
         <f>H13-H14</f>
-        <v>0</v>
+        <v>343831.25</v>
       </c>
       <c r="I15" s="190"/>
       <c r="J15" s="191"/>
@@ -6108,7 +6136,10 @@
       <c r="G16" s="66" t="s">
         <v>43</v>
       </c>
-      <c r="H16" s="149"/>
+      <c r="H16" s="149">
+        <f>334*6</f>
+        <v>2004</v>
+      </c>
       <c r="I16" s="149"/>
       <c r="J16" s="149"/>
       <c r="L16" s="6">
@@ -6302,9 +6333,15 @@
         <f t="shared" si="1"/>
         <v>0</v>
       </c>
-      <c r="F22" s="77"/>
-      <c r="G22" s="73"/>
-      <c r="H22" s="165"/>
+      <c r="F22" s="77" t="s">
+        <v>164</v>
+      </c>
+      <c r="G22" s="73">
+        <v>8425</v>
+      </c>
+      <c r="H22" s="165">
+        <v>100339</v>
+      </c>
       <c r="I22" s="165"/>
       <c r="J22" s="165"/>
       <c r="L22" s="7">
@@ -6432,9 +6469,15 @@
         <f t="shared" si="1"/>
         <v>0</v>
       </c>
-      <c r="F26" s="75"/>
-      <c r="G26" s="65"/>
-      <c r="H26" s="135"/>
+      <c r="F26" s="75" t="s">
+        <v>164</v>
+      </c>
+      <c r="G26" s="65">
+        <v>9125</v>
+      </c>
+      <c r="H26" s="135">
+        <v>98532</v>
+      </c>
       <c r="I26" s="135"/>
       <c r="J26" s="135"/>
       <c r="L26" s="7">
@@ -6490,10 +6533,12 @@
       <c r="B28" s="46" t="s">
         <v>97</v>
       </c>
-      <c r="C28" s="84"/>
+      <c r="C28" s="84">
+        <v>3</v>
+      </c>
       <c r="D28" s="48">
         <f t="shared" si="1"/>
-        <v>0</v>
+        <v>2433</v>
       </c>
       <c r="F28" s="94"/>
       <c r="G28" s="61"/>
@@ -6526,7 +6571,7 @@
       <c r="C29" s="152"/>
       <c r="D29" s="156">
         <f>SUM(D6:D28)</f>
-        <v>0</v>
+        <v>387395</v>
       </c>
       <c r="F29" s="96" t="s">
         <v>55</v>
@@ -6534,7 +6579,7 @@
       <c r="G29" s="158"/>
       <c r="H29" s="118">
         <f>H15-H16-H17-H18-H19-H20-H22-H23-H24+H26+H27+H28</f>
-        <v>0</v>
+        <v>340020.25</v>
       </c>
       <c r="I29" s="119"/>
       <c r="J29" s="120"/>
@@ -6665,18 +6710,22 @@
       <c r="B34" s="26" t="s">
         <v>66</v>
       </c>
-      <c r="C34" s="51"/>
+      <c r="C34" s="51">
+        <v>3</v>
+      </c>
       <c r="D34" s="30">
         <f>C34*120</f>
-        <v>0</v>
+        <v>360</v>
       </c>
       <c r="F34" s="12">
         <v>1000</v>
       </c>
-      <c r="G34" s="40"/>
+      <c r="G34" s="40">
+        <v>10</v>
+      </c>
       <c r="H34" s="140">
         <f t="shared" ref="H34:H39" si="2">F34*G34</f>
-        <v>0</v>
+        <v>10000</v>
       </c>
       <c r="I34" s="141"/>
       <c r="J34" s="142"/>
@@ -6699,10 +6748,12 @@
       <c r="B35" s="27" t="s">
         <v>68</v>
       </c>
-      <c r="C35" s="52"/>
+      <c r="C35" s="52">
+        <v>1</v>
+      </c>
       <c r="D35" s="30">
         <f>C35*84</f>
-        <v>0</v>
+        <v>84</v>
       </c>
       <c r="F35" s="58">
         <v>500</v>
@@ -6731,10 +6782,12 @@
       <c r="B36" s="26" t="s">
         <v>70</v>
       </c>
-      <c r="C36" s="10"/>
+      <c r="C36" s="10">
+        <v>20</v>
+      </c>
       <c r="D36" s="12">
         <f>C36*1.5</f>
-        <v>0</v>
+        <v>30</v>
       </c>
       <c r="F36" s="12">
         <v>200</v>
@@ -6767,18 +6820,22 @@
       <c r="B37" s="28" t="s">
         <v>66</v>
       </c>
-      <c r="C37" s="53"/>
+      <c r="C37" s="53">
+        <v>360</v>
+      </c>
       <c r="D37" s="12">
         <f>C37*111</f>
-        <v>0</v>
+        <v>39960</v>
       </c>
       <c r="F37" s="12">
         <v>100</v>
       </c>
-      <c r="G37" s="39"/>
+      <c r="G37" s="39">
+        <v>1</v>
+      </c>
       <c r="H37" s="140">
         <f t="shared" si="2"/>
-        <v>0</v>
+        <v>100</v>
       </c>
       <c r="I37" s="141"/>
       <c r="J37" s="142"/>
@@ -6801,18 +6858,22 @@
       <c r="B38" s="29" t="s">
         <v>68</v>
       </c>
-      <c r="C38" s="54"/>
+      <c r="C38" s="54">
+        <v>14</v>
+      </c>
       <c r="D38" s="12">
         <f>C38*84</f>
-        <v>0</v>
+        <v>1176</v>
       </c>
       <c r="F38" s="30">
         <v>50</v>
       </c>
-      <c r="G38" s="39"/>
+      <c r="G38" s="39">
+        <v>2</v>
+      </c>
       <c r="H38" s="140">
         <f t="shared" si="2"/>
-        <v>0</v>
+        <v>100</v>
       </c>
       <c r="I38" s="141"/>
       <c r="J38" s="142"/>
@@ -6835,10 +6896,12 @@
       <c r="B39" s="29" t="s">
         <v>70</v>
       </c>
-      <c r="C39" s="52"/>
+      <c r="C39" s="52">
+        <v>3</v>
+      </c>
       <c r="D39" s="31">
         <f>C39*4.5</f>
-        <v>0</v>
+        <v>13.5</v>
       </c>
       <c r="F39" s="12">
         <v>20</v>
@@ -6869,10 +6932,12 @@
       <c r="B40" s="27" t="s">
         <v>66</v>
       </c>
-      <c r="C40" s="63"/>
+      <c r="C40" s="63">
+        <v>8</v>
+      </c>
       <c r="D40" s="12">
         <f>C40*111</f>
-        <v>0</v>
+        <v>888</v>
       </c>
       <c r="F40" s="12">
         <v>10</v>
@@ -6932,15 +6997,19 @@
       <c r="B42" s="27" t="s">
         <v>70</v>
       </c>
-      <c r="C42" s="11"/>
+      <c r="C42" s="11">
+        <v>7</v>
+      </c>
       <c r="D42" s="12">
         <f>C42*2.25</f>
-        <v>0</v>
+        <v>15.75</v>
       </c>
       <c r="F42" s="39" t="s">
         <v>79</v>
       </c>
-      <c r="G42" s="140"/>
+      <c r="G42" s="140">
+        <v>10</v>
+      </c>
       <c r="H42" s="141"/>
       <c r="I42" s="141"/>
       <c r="J42" s="142"/>
@@ -6991,14 +7060,22 @@
       <c r="B44" s="27" t="s">
         <v>66</v>
       </c>
-      <c r="C44" s="10"/>
+      <c r="C44" s="10">
+        <v>4</v>
+      </c>
       <c r="D44" s="12">
         <f>C44*120</f>
-        <v>0</v>
-      </c>
-      <c r="F44" s="37"/>
-      <c r="G44" s="85"/>
-      <c r="H44" s="135"/>
+        <v>480</v>
+      </c>
+      <c r="F44" s="37" t="s">
+        <v>145</v>
+      </c>
+      <c r="G44" s="62" t="s">
+        <v>165</v>
+      </c>
+      <c r="H44" s="135">
+        <v>230441.5</v>
+      </c>
       <c r="I44" s="135"/>
       <c r="J44" s="135"/>
       <c r="K44" s="21"/>
@@ -7026,9 +7103,15 @@
         <f>C45*84</f>
         <v>0</v>
       </c>
-      <c r="F45" s="37"/>
-      <c r="G45" s="62"/>
-      <c r="H45" s="135"/>
+      <c r="F45" s="37" t="s">
+        <v>164</v>
+      </c>
+      <c r="G45" s="62" t="s">
+        <v>166</v>
+      </c>
+      <c r="H45" s="135">
+        <v>98532</v>
+      </c>
       <c r="I45" s="135"/>
       <c r="J45" s="135"/>
       <c r="K45" s="21"/>
@@ -7041,10 +7124,12 @@
       <c r="B46" s="49" t="s">
         <v>70</v>
       </c>
-      <c r="C46" s="81"/>
+      <c r="C46" s="81">
+        <v>2</v>
+      </c>
       <c r="D46" s="12">
         <f>C46*1.5</f>
-        <v>0</v>
+        <v>3</v>
       </c>
       <c r="F46" s="37"/>
       <c r="G46" s="62"/>
@@ -7078,10 +7163,12 @@
       <c r="B48" s="27" t="s">
         <v>66</v>
       </c>
-      <c r="C48" s="10"/>
+      <c r="C48" s="10">
+        <v>3</v>
+      </c>
       <c r="D48" s="12">
         <f>C48*78</f>
-        <v>0</v>
+        <v>234</v>
       </c>
       <c r="F48" s="59"/>
       <c r="G48" s="59"/>
@@ -7106,17 +7193,19 @@
       <c r="B49" s="29" t="s">
         <v>68</v>
       </c>
-      <c r="C49" s="33"/>
+      <c r="C49" s="33">
+        <v>7</v>
+      </c>
       <c r="D49" s="12">
         <f>C49*42</f>
-        <v>0</v>
+        <v>294</v>
       </c>
       <c r="F49" s="116" t="s">
         <v>86</v>
       </c>
       <c r="G49" s="118">
         <f>H34+H35+H36+H37+H38+H39+H40+H41+G42+H44+H45+H46</f>
-        <v>0</v>
+        <v>339183.5</v>
       </c>
       <c r="H49" s="119"/>
       <c r="I49" s="119"/>
@@ -7140,10 +7229,12 @@
       <c r="B50" s="32" t="s">
         <v>70</v>
       </c>
-      <c r="C50" s="11"/>
+      <c r="C50" s="11">
+        <v>17</v>
+      </c>
       <c r="D50" s="12">
         <f>C50*1.5</f>
-        <v>0</v>
+        <v>25.5</v>
       </c>
       <c r="F50" s="117"/>
       <c r="G50" s="121"/>
@@ -7169,7 +7260,7 @@
       </c>
       <c r="G51" s="225">
         <f>G49-H29</f>
-        <v>0</v>
+        <v>-836.75</v>
       </c>
       <c r="H51" s="226"/>
       <c r="I51" s="226"/>
@@ -7240,7 +7331,7 @@
       <c r="C54" s="98"/>
       <c r="D54" s="102">
         <f>SUM(D34:D53)</f>
-        <v>0</v>
+        <v>43563.75</v>
       </c>
       <c r="F54" s="21"/>
       <c r="J54" s="34"/>
@@ -7505,10 +7596,12 @@
       <c r="B6" s="16" t="s">
         <v>15</v>
       </c>
-      <c r="C6" s="10"/>
+      <c r="C6" s="10">
+        <v>326</v>
+      </c>
       <c r="D6" s="13">
         <f t="shared" ref="D6:D28" si="1">C6*L6</f>
-        <v>0</v>
+        <v>248086</v>
       </c>
       <c r="F6" s="203" t="s">
         <v>16</v>
@@ -7711,10 +7804,12 @@
       <c r="B13" s="17" t="s">
         <v>32</v>
       </c>
-      <c r="C13" s="10"/>
+      <c r="C13" s="10">
+        <v>14</v>
+      </c>
       <c r="D13" s="48">
         <f t="shared" si="1"/>
-        <v>0</v>
+        <v>4298</v>
       </c>
       <c r="F13" s="224" t="s">
         <v>36</v>
@@ -7722,7 +7817,7 @@
       <c r="G13" s="188"/>
       <c r="H13" s="179">
         <f>D29</f>
-        <v>0</v>
+        <v>253739</v>
       </c>
       <c r="I13" s="180"/>
       <c r="J13" s="181"/>
@@ -7745,10 +7840,12 @@
       <c r="B14" s="14" t="s">
         <v>35</v>
       </c>
-      <c r="C14" s="10"/>
+      <c r="C14" s="10">
+        <v>5</v>
+      </c>
       <c r="D14" s="31">
         <f t="shared" si="1"/>
-        <v>0</v>
+        <v>55</v>
       </c>
       <c r="F14" s="182" t="s">
         <v>39</v>
@@ -7756,7 +7853,7 @@
       <c r="G14" s="183"/>
       <c r="H14" s="184">
         <f>D54</f>
-        <v>0</v>
+        <v>36819</v>
       </c>
       <c r="I14" s="185"/>
       <c r="J14" s="186"/>
@@ -7794,7 +7891,7 @@
       <c r="G15" s="188"/>
       <c r="H15" s="189">
         <f>H13-H14</f>
-        <v>0</v>
+        <v>216920</v>
       </c>
       <c r="I15" s="190"/>
       <c r="J15" s="191"/>
@@ -7832,7 +7929,10 @@
       <c r="G16" s="66" t="s">
         <v>43</v>
       </c>
-      <c r="H16" s="149"/>
+      <c r="H16" s="149">
+        <f>324*6</f>
+        <v>1944</v>
+      </c>
       <c r="I16" s="149"/>
       <c r="J16" s="149"/>
       <c r="L16" s="6">
@@ -7936,9 +8036,11 @@
       <c r="G19" s="68" t="s">
         <v>50</v>
       </c>
-      <c r="H19" s="235"/>
-      <c r="I19" s="235"/>
-      <c r="J19" s="235"/>
+      <c r="H19" s="149">
+        <v>50</v>
+      </c>
+      <c r="I19" s="149"/>
+      <c r="J19" s="149"/>
       <c r="L19" s="6">
         <f>R35</f>
         <v>1102</v>
@@ -7984,10 +8086,12 @@
       <c r="B21" s="14" t="s">
         <v>131</v>
       </c>
-      <c r="C21" s="10"/>
+      <c r="C21" s="10">
+        <v>2</v>
+      </c>
       <c r="D21" s="48">
         <f t="shared" si="1"/>
-        <v>0</v>
+        <v>1300</v>
       </c>
       <c r="F21" s="69" t="s">
         <v>99</v>
@@ -8253,7 +8357,7 @@
       <c r="C29" s="152"/>
       <c r="D29" s="156">
         <f>SUM(D6:D28)</f>
-        <v>0</v>
+        <v>253739</v>
       </c>
       <c r="F29" s="96" t="s">
         <v>55</v>
@@ -8261,7 +8365,7 @@
       <c r="G29" s="158"/>
       <c r="H29" s="118">
         <f>H15-H16-H17-H18-H19-H20-H22-H23-H24+H26+H27</f>
-        <v>0</v>
+        <v>214926</v>
       </c>
       <c r="I29" s="119"/>
       <c r="J29" s="120"/>
@@ -8400,10 +8504,12 @@
       <c r="F34" s="12">
         <v>1000</v>
       </c>
-      <c r="G34" s="74"/>
+      <c r="G34" s="74">
+        <v>214</v>
+      </c>
       <c r="H34" s="140">
         <f>F34*G34</f>
-        <v>0</v>
+        <v>214000</v>
       </c>
       <c r="I34" s="141"/>
       <c r="J34" s="142"/>
@@ -8434,10 +8540,12 @@
       <c r="F35" s="58">
         <v>500</v>
       </c>
-      <c r="G35" s="41"/>
+      <c r="G35" s="41">
+        <v>1</v>
+      </c>
       <c r="H35" s="140">
         <f t="shared" ref="H35:H39" si="2">F35*G35</f>
-        <v>0</v>
+        <v>500</v>
       </c>
       <c r="I35" s="141"/>
       <c r="J35" s="142"/>
@@ -8494,18 +8602,22 @@
       <c r="B37" s="28" t="s">
         <v>66</v>
       </c>
-      <c r="C37" s="53"/>
+      <c r="C37" s="53">
+        <v>325</v>
+      </c>
       <c r="D37" s="12">
         <f>C37*111</f>
-        <v>0</v>
+        <v>36075</v>
       </c>
       <c r="F37" s="12">
         <v>100</v>
       </c>
-      <c r="G37" s="39"/>
+      <c r="G37" s="39">
+        <v>3</v>
+      </c>
       <c r="H37" s="140">
         <f t="shared" si="2"/>
-        <v>0</v>
+        <v>300</v>
       </c>
       <c r="I37" s="141"/>
       <c r="J37" s="142"/>
@@ -8528,18 +8640,22 @@
       <c r="B38" s="29" t="s">
         <v>68</v>
       </c>
-      <c r="C38" s="54"/>
+      <c r="C38" s="54">
+        <v>1</v>
+      </c>
       <c r="D38" s="12">
         <f>C38*84</f>
-        <v>0</v>
+        <v>84</v>
       </c>
       <c r="F38" s="30">
         <v>50</v>
       </c>
-      <c r="G38" s="39"/>
+      <c r="G38" s="39">
+        <v>1</v>
+      </c>
       <c r="H38" s="140">
         <f t="shared" si="2"/>
-        <v>0</v>
+        <v>50</v>
       </c>
       <c r="I38" s="141"/>
       <c r="J38" s="142"/>
@@ -8562,10 +8678,12 @@
       <c r="B39" s="29" t="s">
         <v>70</v>
       </c>
-      <c r="C39" s="52"/>
+      <c r="C39" s="52">
+        <v>1</v>
+      </c>
       <c r="D39" s="31">
         <f>C39*4.5</f>
-        <v>0</v>
+        <v>4.5</v>
       </c>
       <c r="F39" s="12">
         <v>20</v>
@@ -8667,7 +8785,9 @@
       <c r="F42" s="39" t="s">
         <v>79</v>
       </c>
-      <c r="G42" s="140"/>
+      <c r="G42" s="140">
+        <v>32</v>
+      </c>
       <c r="H42" s="141"/>
       <c r="I42" s="141"/>
       <c r="J42" s="142"/>
@@ -8805,10 +8925,12 @@
       <c r="B48" s="27" t="s">
         <v>66</v>
       </c>
-      <c r="C48" s="10"/>
+      <c r="C48" s="10">
+        <v>3</v>
+      </c>
       <c r="D48" s="12">
         <f>C48*78</f>
-        <v>0</v>
+        <v>234</v>
       </c>
       <c r="F48" s="59"/>
       <c r="G48" s="59"/>
@@ -8833,17 +8955,19 @@
       <c r="B49" s="29" t="s">
         <v>68</v>
       </c>
-      <c r="C49" s="33"/>
+      <c r="C49" s="33">
+        <v>10</v>
+      </c>
       <c r="D49" s="12">
         <f>C49*42</f>
-        <v>0</v>
+        <v>420</v>
       </c>
       <c r="F49" s="116" t="s">
         <v>86</v>
       </c>
       <c r="G49" s="118">
         <f>H34+H35+H36+H37+H38+H39+H40+H41+G42+H44+H45+H46</f>
-        <v>0</v>
+        <v>214882</v>
       </c>
       <c r="H49" s="119"/>
       <c r="I49" s="119"/>
@@ -8867,10 +8991,12 @@
       <c r="B50" s="32" t="s">
         <v>70</v>
       </c>
-      <c r="C50" s="11"/>
+      <c r="C50" s="11">
+        <v>1</v>
+      </c>
       <c r="D50" s="12">
         <f>C50*1.5</f>
-        <v>0</v>
+        <v>1.5</v>
       </c>
       <c r="F50" s="117"/>
       <c r="G50" s="121"/>
@@ -8892,15 +9018,15 @@
       <c r="C51" s="10"/>
       <c r="D51" s="31"/>
       <c r="F51" s="124" t="s">
-        <v>135</v>
-      </c>
-      <c r="G51" s="126">
+        <v>162</v>
+      </c>
+      <c r="G51" s="225">
         <f>G49-H29</f>
-        <v>0</v>
-      </c>
-      <c r="H51" s="127"/>
-      <c r="I51" s="127"/>
-      <c r="J51" s="128"/>
+        <v>-44</v>
+      </c>
+      <c r="H51" s="226"/>
+      <c r="I51" s="226"/>
+      <c r="J51" s="227"/>
       <c r="K51" s="21"/>
       <c r="O51" t="s">
         <v>87</v>
@@ -8922,10 +9048,10 @@
       <c r="C52" s="33"/>
       <c r="D52" s="45"/>
       <c r="F52" s="125"/>
-      <c r="G52" s="129"/>
-      <c r="H52" s="130"/>
-      <c r="I52" s="130"/>
-      <c r="J52" s="131"/>
+      <c r="G52" s="228"/>
+      <c r="H52" s="229"/>
+      <c r="I52" s="229"/>
+      <c r="J52" s="230"/>
       <c r="K52" s="21"/>
       <c r="O52" t="s">
         <v>88</v>
@@ -8967,7 +9093,7 @@
       <c r="C54" s="98"/>
       <c r="D54" s="102">
         <f>SUM(D34:D53)</f>
-        <v>0</v>
+        <v>36819</v>
       </c>
       <c r="F54" s="21"/>
       <c r="J54" s="34"/>
@@ -9232,10 +9358,12 @@
       <c r="B6" s="16" t="s">
         <v>15</v>
       </c>
-      <c r="C6" s="10"/>
+      <c r="C6" s="10">
+        <v>270</v>
+      </c>
       <c r="D6" s="13">
         <f t="shared" ref="D6:D28" si="1">C6*L6</f>
-        <v>0</v>
+        <v>205470</v>
       </c>
       <c r="F6" s="203" t="s">
         <v>16</v>
@@ -9320,10 +9448,12 @@
       <c r="B9" s="16" t="s">
         <v>23</v>
       </c>
-      <c r="C9" s="10"/>
+      <c r="C9" s="10">
+        <v>29</v>
+      </c>
       <c r="D9" s="13">
         <f t="shared" si="1"/>
-        <v>0</v>
+        <v>21257</v>
       </c>
       <c r="F9" s="204"/>
       <c r="G9" s="215"/>
@@ -9438,10 +9568,12 @@
       <c r="B13" s="17" t="s">
         <v>32</v>
       </c>
-      <c r="C13" s="10"/>
+      <c r="C13" s="10">
+        <v>8</v>
+      </c>
       <c r="D13" s="48">
         <f t="shared" si="1"/>
-        <v>0</v>
+        <v>2456</v>
       </c>
       <c r="F13" s="224" t="s">
         <v>36</v>
@@ -9449,7 +9581,7 @@
       <c r="G13" s="188"/>
       <c r="H13" s="179">
         <f>D29</f>
-        <v>0</v>
+        <v>236285</v>
       </c>
       <c r="I13" s="180"/>
       <c r="J13" s="181"/>
@@ -9472,10 +9604,12 @@
       <c r="B14" s="14" t="s">
         <v>35</v>
       </c>
-      <c r="C14" s="10"/>
+      <c r="C14" s="10">
+        <v>7</v>
+      </c>
       <c r="D14" s="31">
         <f t="shared" si="1"/>
-        <v>0</v>
+        <v>77</v>
       </c>
       <c r="F14" s="182" t="s">
         <v>39</v>
@@ -9483,7 +9617,7 @@
       <c r="G14" s="183"/>
       <c r="H14" s="184">
         <f>D54</f>
-        <v>0</v>
+        <v>33749.25</v>
       </c>
       <c r="I14" s="185"/>
       <c r="J14" s="186"/>
@@ -9521,7 +9655,7 @@
       <c r="G15" s="188"/>
       <c r="H15" s="189">
         <f>H13-H14</f>
-        <v>0</v>
+        <v>202535.75</v>
       </c>
       <c r="I15" s="190"/>
       <c r="J15" s="191"/>
@@ -9559,7 +9693,10 @@
       <c r="G16" s="66" t="s">
         <v>43</v>
       </c>
-      <c r="H16" s="149"/>
+      <c r="H16" s="149">
+        <f>50*6+80*6+63*6</f>
+        <v>1158</v>
+      </c>
       <c r="I16" s="149"/>
       <c r="J16" s="149"/>
       <c r="L16" s="6">
@@ -9662,9 +9799,11 @@
       <c r="G19" s="68" t="s">
         <v>50</v>
       </c>
-      <c r="H19" s="236"/>
-      <c r="I19" s="236"/>
-      <c r="J19" s="236"/>
+      <c r="H19" s="149">
+        <v>50</v>
+      </c>
+      <c r="I19" s="149"/>
+      <c r="J19" s="149"/>
       <c r="L19" s="6">
         <f>R35</f>
         <v>1102</v>
@@ -9710,10 +9849,12 @@
       <c r="B21" s="14" t="s">
         <v>123</v>
       </c>
-      <c r="C21" s="10"/>
+      <c r="C21" s="10">
+        <v>9</v>
+      </c>
       <c r="D21" s="48">
         <f t="shared" si="1"/>
-        <v>0</v>
+        <v>5850</v>
       </c>
       <c r="F21" s="69" t="s">
         <v>99</v>
@@ -9779,10 +9920,12 @@
       <c r="B23" s="14" t="s">
         <v>107</v>
       </c>
-      <c r="C23" s="10"/>
+      <c r="C23" s="10">
+        <v>1</v>
+      </c>
       <c r="D23" s="48">
         <f t="shared" si="1"/>
-        <v>0</v>
+        <v>1175</v>
       </c>
       <c r="F23" s="78"/>
       <c r="G23" s="79"/>
@@ -9978,7 +10121,7 @@
       <c r="C29" s="152"/>
       <c r="D29" s="156">
         <f>SUM(D6:D28)</f>
-        <v>0</v>
+        <v>236285</v>
       </c>
       <c r="F29" s="96" t="s">
         <v>55</v>
@@ -9986,7 +10129,7 @@
       <c r="G29" s="158"/>
       <c r="H29" s="118">
         <f>H15-H16-H17-H18-H19-H20-H22-H23-H24+H26+H27</f>
-        <v>0</v>
+        <v>201327.75</v>
       </c>
       <c r="I29" s="119"/>
       <c r="J29" s="120"/>
@@ -10125,10 +10268,12 @@
       <c r="F34" s="12">
         <v>1000</v>
       </c>
-      <c r="G34" s="74"/>
+      <c r="G34" s="74">
+        <v>94</v>
+      </c>
       <c r="H34" s="140">
         <f>F34*G34</f>
-        <v>0</v>
+        <v>94000</v>
       </c>
       <c r="I34" s="141"/>
       <c r="J34" s="142"/>
@@ -10159,10 +10304,12 @@
       <c r="F35" s="58">
         <v>500</v>
       </c>
-      <c r="G35" s="41"/>
+      <c r="G35" s="41">
+        <v>108</v>
+      </c>
       <c r="H35" s="140">
         <f>F35*G35</f>
-        <v>0</v>
+        <v>54000</v>
       </c>
       <c r="I35" s="141"/>
       <c r="J35" s="142"/>
@@ -10219,18 +10366,22 @@
       <c r="B37" s="28" t="s">
         <v>66</v>
       </c>
-      <c r="C37" s="53"/>
+      <c r="C37" s="53">
+        <v>297</v>
+      </c>
       <c r="D37" s="12">
         <f>C37*111</f>
-        <v>0</v>
+        <v>32967</v>
       </c>
       <c r="F37" s="12">
         <v>100</v>
       </c>
-      <c r="G37" s="39"/>
+      <c r="G37" s="39">
+        <v>124</v>
+      </c>
       <c r="H37" s="140">
         <f t="shared" si="2"/>
-        <v>0</v>
+        <v>12400</v>
       </c>
       <c r="I37" s="141"/>
       <c r="J37" s="142"/>
@@ -10253,18 +10404,22 @@
       <c r="B38" s="29" t="s">
         <v>68</v>
       </c>
-      <c r="C38" s="54"/>
+      <c r="C38" s="54">
+        <v>2</v>
+      </c>
       <c r="D38" s="12">
         <f>C38*84</f>
-        <v>0</v>
+        <v>168</v>
       </c>
       <c r="F38" s="30">
         <v>50</v>
       </c>
-      <c r="G38" s="39"/>
+      <c r="G38" s="39">
+        <v>2</v>
+      </c>
       <c r="H38" s="140">
         <f t="shared" si="2"/>
-        <v>0</v>
+        <v>100</v>
       </c>
       <c r="I38" s="141"/>
       <c r="J38" s="142"/>
@@ -10287,10 +10442,12 @@
       <c r="B39" s="29" t="s">
         <v>70</v>
       </c>
-      <c r="C39" s="52"/>
+      <c r="C39" s="52">
+        <v>2</v>
+      </c>
       <c r="D39" s="31">
         <f>C39*4.5</f>
-        <v>0</v>
+        <v>9</v>
       </c>
       <c r="F39" s="12">
         <v>20</v>
@@ -10384,15 +10541,19 @@
       <c r="B42" s="27" t="s">
         <v>70</v>
       </c>
-      <c r="C42" s="11"/>
+      <c r="C42" s="11">
+        <v>17</v>
+      </c>
       <c r="D42" s="12">
         <f>C42*2.25</f>
-        <v>0</v>
+        <v>38.25</v>
       </c>
       <c r="F42" s="39" t="s">
         <v>79</v>
       </c>
-      <c r="G42" s="140"/>
+      <c r="G42" s="140">
+        <v>94</v>
+      </c>
       <c r="H42" s="141"/>
       <c r="I42" s="141"/>
       <c r="J42" s="142"/>
@@ -10448,9 +10609,15 @@
         <f>C44*120</f>
         <v>0</v>
       </c>
-      <c r="F44" s="37"/>
-      <c r="G44" s="76"/>
-      <c r="H44" s="135"/>
+      <c r="F44" s="37" t="s">
+        <v>145</v>
+      </c>
+      <c r="G44" s="62" t="s">
+        <v>163</v>
+      </c>
+      <c r="H44" s="135">
+        <v>40666</v>
+      </c>
       <c r="I44" s="135"/>
       <c r="J44" s="135"/>
       <c r="K44" s="21"/>
@@ -10530,10 +10697,12 @@
       <c r="B48" s="27" t="s">
         <v>66</v>
       </c>
-      <c r="C48" s="10"/>
+      <c r="C48" s="10">
+        <v>5</v>
+      </c>
       <c r="D48" s="12">
         <f>C48*78</f>
-        <v>0</v>
+        <v>390</v>
       </c>
       <c r="F48" s="59"/>
       <c r="G48" s="59"/>
@@ -10558,17 +10727,19 @@
       <c r="B49" s="29" t="s">
         <v>68</v>
       </c>
-      <c r="C49" s="33"/>
+      <c r="C49" s="33">
+        <v>4</v>
+      </c>
       <c r="D49" s="12">
         <f>C49*42</f>
-        <v>0</v>
+        <v>168</v>
       </c>
       <c r="F49" s="116" t="s">
         <v>86</v>
       </c>
       <c r="G49" s="118">
         <f>H34+H35+H36+H37+H38+H39+H40+H41+G42+H44+H45+H46</f>
-        <v>0</v>
+        <v>201260</v>
       </c>
       <c r="H49" s="119"/>
       <c r="I49" s="119"/>
@@ -10592,10 +10763,12 @@
       <c r="B50" s="32" t="s">
         <v>70</v>
       </c>
-      <c r="C50" s="11"/>
+      <c r="C50" s="11">
+        <v>6</v>
+      </c>
       <c r="D50" s="12">
         <f>C50*1.5</f>
-        <v>0</v>
+        <v>9</v>
       </c>
       <c r="F50" s="117"/>
       <c r="G50" s="121"/>
@@ -10617,15 +10790,15 @@
       <c r="C51" s="10"/>
       <c r="D51" s="31"/>
       <c r="F51" s="124" t="s">
-        <v>138</v>
-      </c>
-      <c r="G51" s="126">
+        <v>128</v>
+      </c>
+      <c r="G51" s="225">
         <f>G49-H29</f>
-        <v>0</v>
-      </c>
-      <c r="H51" s="127"/>
-      <c r="I51" s="127"/>
-      <c r="J51" s="128"/>
+        <v>-67.75</v>
+      </c>
+      <c r="H51" s="226"/>
+      <c r="I51" s="226"/>
+      <c r="J51" s="227"/>
       <c r="K51" s="21"/>
       <c r="O51" t="s">
         <v>87</v>
@@ -10647,10 +10820,10 @@
       <c r="C52" s="33"/>
       <c r="D52" s="45"/>
       <c r="F52" s="125"/>
-      <c r="G52" s="129"/>
-      <c r="H52" s="130"/>
-      <c r="I52" s="130"/>
-      <c r="J52" s="131"/>
+      <c r="G52" s="228"/>
+      <c r="H52" s="229"/>
+      <c r="I52" s="229"/>
+      <c r="J52" s="230"/>
       <c r="K52" s="21"/>
       <c r="O52" t="s">
         <v>88</v>
@@ -10692,7 +10865,7 @@
       <c r="C54" s="98"/>
       <c r="D54" s="102">
         <f>SUM(D34:D53)</f>
-        <v>0</v>
+        <v>33749.25</v>
       </c>
       <c r="F54" s="21"/>
       <c r="J54" s="34"/>

--- a/GBDS MARCH FILES 2026/SCRR CALCULATOR - MARCH 2026.xlsx
+++ b/GBDS MARCH FILES 2026/SCRR CALCULATOR - MARCH 2026.xlsx
@@ -8,9 +8,9 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Users\User\Desktop\GBDS MARCH FILES 2026\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{F8242A74-5E27-4248-91D8-BBB5DEE8341C}" xr6:coauthVersionLast="45" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{1D1F633F-F17D-4E5B-AE4F-9D2F635E72BA}" xr6:coauthVersionLast="45" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
-    <workbookView xWindow="-120" yWindow="-120" windowWidth="29040" windowHeight="15840" firstSheet="11" activeTab="20" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
+    <workbookView xWindow="-120" yWindow="-120" windowWidth="29040" windowHeight="15840" firstSheet="17" activeTab="22" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
   <sheets>
     <sheet name="(March 2026)" sheetId="814" r:id="rId1"/>
@@ -89,7 +89,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="3782" uniqueCount="172">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="3785" uniqueCount="175">
   <si>
     <t>GUILLERMO BEVERAGE DISTRIBUTION SERVICES</t>
   </si>
@@ -729,6 +729,15 @@
   </si>
   <si>
     <t>42996</t>
+  </si>
+  <si>
+    <t>PSBC</t>
+  </si>
+  <si>
+    <t>2120012901</t>
+  </si>
+  <si>
+    <t>SOUND CHECK</t>
   </si>
 </sst>
 </file>
@@ -1618,7 +1627,7 @@
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0"/>
     <xf numFmtId="43" fontId="1" fillId="0" borderId="0" applyFont="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0"/>
   </cellStyleXfs>
-  <cellXfs count="238">
+  <cellXfs count="239">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0"/>
     <xf numFmtId="0" fontId="2" fillId="0" borderId="0" xfId="0" applyFont="1"/>
     <xf numFmtId="0" fontId="2" fillId="2" borderId="0" xfId="0" applyFont="1" applyFill="1" applyAlignment="1">
@@ -2215,6 +2224,9 @@
       <alignment horizontal="right"/>
     </xf>
     <xf numFmtId="44" fontId="12" fillId="3" borderId="16" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="right"/>
+    </xf>
+    <xf numFmtId="49" fontId="0" fillId="0" borderId="16" xfId="0" applyNumberFormat="1" applyFont="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="right"/>
     </xf>
   </cellXfs>
@@ -28109,10 +28121,12 @@
       <c r="B6" s="16" t="s">
         <v>15</v>
       </c>
-      <c r="C6" s="84"/>
+      <c r="C6" s="84">
+        <v>319</v>
+      </c>
       <c r="D6" s="13">
         <f t="shared" ref="D6:D28" si="1">C6*L6</f>
-        <v>0</v>
+        <v>242759</v>
       </c>
       <c r="F6" s="204" t="s">
         <v>16</v>
@@ -28169,10 +28183,12 @@
       <c r="B8" s="16" t="s">
         <v>20</v>
       </c>
-      <c r="C8" s="84"/>
+      <c r="C8" s="84">
+        <v>50</v>
+      </c>
       <c r="D8" s="13">
         <f t="shared" si="1"/>
-        <v>0</v>
+        <v>54650</v>
       </c>
       <c r="F8" s="212" t="s">
         <v>21</v>
@@ -28197,10 +28213,12 @@
       <c r="B9" s="16" t="s">
         <v>23</v>
       </c>
-      <c r="C9" s="84"/>
+      <c r="C9" s="84">
+        <v>17</v>
+      </c>
       <c r="D9" s="13">
         <f t="shared" si="1"/>
-        <v>0</v>
+        <v>12461</v>
       </c>
       <c r="F9" s="205"/>
       <c r="G9" s="216"/>
@@ -28249,10 +28267,12 @@
       <c r="B11" s="17" t="s">
         <v>28</v>
       </c>
-      <c r="C11" s="84"/>
+      <c r="C11" s="84">
+        <v>2</v>
+      </c>
       <c r="D11" s="13">
         <f t="shared" si="1"/>
-        <v>0</v>
+        <v>2340</v>
       </c>
       <c r="F11" s="205"/>
       <c r="G11" s="216"/>
@@ -28281,10 +28301,12 @@
       <c r="B12" s="17" t="s">
         <v>30</v>
       </c>
-      <c r="C12" s="84"/>
+      <c r="C12" s="84">
+        <v>1</v>
+      </c>
       <c r="D12" s="48">
         <f t="shared" si="1"/>
-        <v>0</v>
+        <v>992</v>
       </c>
       <c r="F12" s="222" t="s">
         <v>33</v>
@@ -28315,10 +28337,12 @@
       <c r="B13" s="17" t="s">
         <v>32</v>
       </c>
-      <c r="C13" s="84"/>
+      <c r="C13" s="84">
+        <v>1</v>
+      </c>
       <c r="D13" s="48">
         <f t="shared" si="1"/>
-        <v>0</v>
+        <v>307</v>
       </c>
       <c r="F13" s="225" t="s">
         <v>36</v>
@@ -28326,7 +28350,7 @@
       <c r="G13" s="189"/>
       <c r="H13" s="180">
         <f>D29</f>
-        <v>0</v>
+        <v>319434</v>
       </c>
       <c r="I13" s="181"/>
       <c r="J13" s="182"/>
@@ -28360,7 +28384,7 @@
       <c r="G14" s="184"/>
       <c r="H14" s="185">
         <f>D54</f>
-        <v>0</v>
+        <v>42474.75</v>
       </c>
       <c r="I14" s="186"/>
       <c r="J14" s="187"/>
@@ -28398,7 +28422,7 @@
       <c r="G15" s="189"/>
       <c r="H15" s="190">
         <f>H13-H14</f>
-        <v>0</v>
+        <v>276959.25</v>
       </c>
       <c r="I15" s="191"/>
       <c r="J15" s="192"/>
@@ -28462,10 +28486,12 @@
       <c r="B17" t="s">
         <v>133</v>
       </c>
-      <c r="C17" s="84"/>
+      <c r="C17" s="84">
+        <v>2</v>
+      </c>
       <c r="D17" s="48">
         <f t="shared" si="1"/>
-        <v>0</v>
+        <v>3164</v>
       </c>
       <c r="F17" s="56"/>
       <c r="G17" s="66" t="s">
@@ -28587,10 +28613,13 @@
       <c r="B21" s="14" t="s">
         <v>131</v>
       </c>
-      <c r="C21" s="84"/>
+      <c r="C21" s="84">
+        <f>2+1</f>
+        <v>3</v>
+      </c>
       <c r="D21" s="48">
         <f t="shared" si="1"/>
-        <v>0</v>
+        <v>1950</v>
       </c>
       <c r="F21" s="69" t="s">
         <v>99</v>
@@ -28630,9 +28659,15 @@
         <f t="shared" si="1"/>
         <v>0</v>
       </c>
-      <c r="F22" s="77"/>
-      <c r="G22" s="73"/>
-      <c r="H22" s="166"/>
+      <c r="F22" s="77" t="s">
+        <v>174</v>
+      </c>
+      <c r="G22" s="73">
+        <v>9435</v>
+      </c>
+      <c r="H22" s="166">
+        <v>51622</v>
+      </c>
       <c r="I22" s="166"/>
       <c r="J22" s="166"/>
       <c r="L22" s="7">
@@ -28818,10 +28853,12 @@
       <c r="B28" s="46" t="s">
         <v>97</v>
       </c>
-      <c r="C28" s="84"/>
+      <c r="C28" s="84">
+        <v>1</v>
+      </c>
       <c r="D28" s="48">
         <f t="shared" si="1"/>
-        <v>0</v>
+        <v>811</v>
       </c>
       <c r="F28" s="94"/>
       <c r="G28" s="61"/>
@@ -28854,7 +28891,7 @@
       <c r="C29" s="153"/>
       <c r="D29" s="157">
         <f>SUM(D6:D28)</f>
-        <v>0</v>
+        <v>319434</v>
       </c>
       <c r="F29" s="97" t="s">
         <v>55</v>
@@ -28862,7 +28899,7 @@
       <c r="G29" s="159"/>
       <c r="H29" s="119">
         <f>H15-H16-H17-H18-H19-H20-H22-H23-H24+H26+H27+H28</f>
-        <v>0</v>
+        <v>225337.25</v>
       </c>
       <c r="I29" s="120"/>
       <c r="J29" s="121"/>
@@ -28993,18 +29030,22 @@
       <c r="B34" s="26" t="s">
         <v>66</v>
       </c>
-      <c r="C34" s="51"/>
+      <c r="C34" s="51">
+        <v>1</v>
+      </c>
       <c r="D34" s="30">
         <f>C34*120</f>
-        <v>0</v>
+        <v>120</v>
       </c>
       <c r="F34" s="12">
         <v>1000</v>
       </c>
-      <c r="G34" s="40"/>
+      <c r="G34" s="40">
+        <v>82</v>
+      </c>
       <c r="H34" s="141">
         <f t="shared" ref="H34:H39" si="2">F34*G34</f>
-        <v>0</v>
+        <v>82000</v>
       </c>
       <c r="I34" s="142"/>
       <c r="J34" s="143"/>
@@ -29059,10 +29100,12 @@
       <c r="B36" s="26" t="s">
         <v>70</v>
       </c>
-      <c r="C36" s="10"/>
+      <c r="C36" s="10">
+        <v>2</v>
+      </c>
       <c r="D36" s="12">
         <f>C36*1.5</f>
-        <v>0</v>
+        <v>3</v>
       </c>
       <c r="F36" s="12">
         <v>200</v>
@@ -29095,18 +29138,22 @@
       <c r="B37" s="28" t="s">
         <v>66</v>
       </c>
-      <c r="C37" s="53"/>
+      <c r="C37" s="53">
+        <v>317</v>
+      </c>
       <c r="D37" s="12">
         <f>C37*111</f>
-        <v>0</v>
+        <v>35187</v>
       </c>
       <c r="F37" s="12">
         <v>100</v>
       </c>
-      <c r="G37" s="39"/>
+      <c r="G37" s="39">
+        <v>2</v>
+      </c>
       <c r="H37" s="141">
         <f t="shared" si="2"/>
-        <v>0</v>
+        <v>200</v>
       </c>
       <c r="I37" s="142"/>
       <c r="J37" s="143"/>
@@ -29129,18 +29176,22 @@
       <c r="B38" s="29" t="s">
         <v>68</v>
       </c>
-      <c r="C38" s="54"/>
+      <c r="C38" s="54">
+        <v>1</v>
+      </c>
       <c r="D38" s="12">
         <f>C38*84</f>
-        <v>0</v>
+        <v>84</v>
       </c>
       <c r="F38" s="30">
         <v>50</v>
       </c>
-      <c r="G38" s="39"/>
+      <c r="G38" s="39">
+        <v>1</v>
+      </c>
       <c r="H38" s="141">
         <f t="shared" si="2"/>
-        <v>0</v>
+        <v>50</v>
       </c>
       <c r="I38" s="142"/>
       <c r="J38" s="143"/>
@@ -29197,10 +29248,12 @@
       <c r="B40" s="27" t="s">
         <v>66</v>
       </c>
-      <c r="C40" s="63"/>
+      <c r="C40" s="63">
+        <v>62</v>
+      </c>
       <c r="D40" s="12">
         <f>C40*111</f>
-        <v>0</v>
+        <v>6882</v>
       </c>
       <c r="F40" s="12">
         <v>10</v>
@@ -29228,10 +29281,12 @@
       <c r="B41" s="27" t="s">
         <v>68</v>
       </c>
-      <c r="C41" s="10"/>
+      <c r="C41" s="10">
+        <v>1</v>
+      </c>
       <c r="D41" s="12">
         <f>C41*84</f>
-        <v>0</v>
+        <v>84</v>
       </c>
       <c r="F41" s="12">
         <v>5</v>
@@ -29260,15 +29315,19 @@
       <c r="B42" s="27" t="s">
         <v>70</v>
       </c>
-      <c r="C42" s="11"/>
+      <c r="C42" s="11">
+        <v>9</v>
+      </c>
       <c r="D42" s="12">
         <f>C42*2.25</f>
-        <v>0</v>
+        <v>20.25</v>
       </c>
       <c r="F42" s="39" t="s">
         <v>79</v>
       </c>
-      <c r="G42" s="141"/>
+      <c r="G42" s="141">
+        <v>106</v>
+      </c>
       <c r="H42" s="142"/>
       <c r="I42" s="142"/>
       <c r="J42" s="143"/>
@@ -29324,9 +29383,15 @@
         <f>C44*120</f>
         <v>0</v>
       </c>
-      <c r="F44" s="37"/>
-      <c r="G44" s="85"/>
-      <c r="H44" s="136"/>
+      <c r="F44" s="37" t="s">
+        <v>172</v>
+      </c>
+      <c r="G44" s="238" t="s">
+        <v>173</v>
+      </c>
+      <c r="H44" s="136">
+        <v>141334</v>
+      </c>
       <c r="I44" s="136"/>
       <c r="J44" s="136"/>
       <c r="K44" s="21"/>
@@ -29369,10 +29434,12 @@
       <c r="B46" s="49" t="s">
         <v>70</v>
       </c>
-      <c r="C46" s="81"/>
+      <c r="C46" s="81">
+        <v>3</v>
+      </c>
       <c r="D46" s="12">
         <f>C46*1.5</f>
-        <v>0</v>
+        <v>4.5</v>
       </c>
       <c r="F46" s="37"/>
       <c r="G46" s="62"/>
@@ -29406,10 +29473,12 @@
       <c r="B48" s="27" t="s">
         <v>66</v>
       </c>
-      <c r="C48" s="10"/>
+      <c r="C48" s="10">
+        <v>1</v>
+      </c>
       <c r="D48" s="12">
         <f>C48*78</f>
-        <v>0</v>
+        <v>78</v>
       </c>
       <c r="F48" s="59"/>
       <c r="G48" s="59"/>
@@ -29444,7 +29513,7 @@
       </c>
       <c r="G49" s="119">
         <f>H34+H35+H36+H37+H38+H39+H40+H41+G42+H44+H45+H46</f>
-        <v>0</v>
+        <v>223690</v>
       </c>
       <c r="H49" s="120"/>
       <c r="I49" s="120"/>
@@ -29468,10 +29537,12 @@
       <c r="B50" s="32" t="s">
         <v>70</v>
       </c>
-      <c r="C50" s="11"/>
+      <c r="C50" s="11">
+        <v>8</v>
+      </c>
       <c r="D50" s="12">
         <f>C50*1.5</f>
-        <v>0</v>
+        <v>12</v>
       </c>
       <c r="F50" s="118"/>
       <c r="G50" s="122"/>
@@ -29497,7 +29568,7 @@
       </c>
       <c r="G51" s="226">
         <f>G49-H29</f>
-        <v>0</v>
+        <v>-1647.25</v>
       </c>
       <c r="H51" s="227"/>
       <c r="I51" s="227"/>
@@ -29568,7 +29639,7 @@
       <c r="C54" s="99"/>
       <c r="D54" s="103">
         <f>SUM(D34:D53)</f>
-        <v>0</v>
+        <v>42474.75</v>
       </c>
       <c r="F54" s="21"/>
       <c r="J54" s="34"/>
@@ -29833,10 +29904,12 @@
       <c r="B6" s="16" t="s">
         <v>15</v>
       </c>
-      <c r="C6" s="10"/>
+      <c r="C6" s="10">
+        <v>385</v>
+      </c>
       <c r="D6" s="13">
         <f t="shared" ref="D6:D28" si="1">C6*L6</f>
-        <v>0</v>
+        <v>292985</v>
       </c>
       <c r="F6" s="204" t="s">
         <v>16</v>
@@ -29869,10 +29942,12 @@
       <c r="B7" s="16" t="s">
         <v>18</v>
       </c>
-      <c r="C7" s="10"/>
+      <c r="C7" s="10">
+        <v>4</v>
+      </c>
       <c r="D7" s="13">
         <f t="shared" si="1"/>
-        <v>0</v>
+        <v>3124</v>
       </c>
       <c r="F7" s="205"/>
       <c r="G7" s="209"/>
@@ -29921,10 +29996,12 @@
       <c r="B9" s="16" t="s">
         <v>23</v>
       </c>
-      <c r="C9" s="10"/>
+      <c r="C9" s="10">
+        <v>68</v>
+      </c>
       <c r="D9" s="13">
         <f t="shared" si="1"/>
-        <v>0</v>
+        <v>49844</v>
       </c>
       <c r="F9" s="205"/>
       <c r="G9" s="216"/>
@@ -30005,10 +30082,12 @@
       <c r="B12" s="17" t="s">
         <v>30</v>
       </c>
-      <c r="C12" s="10"/>
+      <c r="C12" s="10">
+        <v>2</v>
+      </c>
       <c r="D12" s="48">
         <f t="shared" si="1"/>
-        <v>0</v>
+        <v>1984</v>
       </c>
       <c r="F12" s="222" t="s">
         <v>33</v>
@@ -30039,10 +30118,12 @@
       <c r="B13" s="17" t="s">
         <v>32</v>
       </c>
-      <c r="C13" s="10"/>
+      <c r="C13" s="10">
+        <v>10</v>
+      </c>
       <c r="D13" s="48">
         <f t="shared" si="1"/>
-        <v>0</v>
+        <v>3070</v>
       </c>
       <c r="F13" s="225" t="s">
         <v>36</v>
@@ -30050,7 +30131,7 @@
       <c r="G13" s="189"/>
       <c r="H13" s="180">
         <f>D29</f>
-        <v>0</v>
+        <v>351657</v>
       </c>
       <c r="I13" s="181"/>
       <c r="J13" s="182"/>
@@ -30084,7 +30165,7 @@
       <c r="G14" s="184"/>
       <c r="H14" s="185">
         <f>D54</f>
-        <v>0</v>
+        <v>33426</v>
       </c>
       <c r="I14" s="186"/>
       <c r="J14" s="187"/>
@@ -30122,7 +30203,7 @@
       <c r="G15" s="189"/>
       <c r="H15" s="190">
         <f>H13-H14</f>
-        <v>0</v>
+        <v>318231</v>
       </c>
       <c r="I15" s="191"/>
       <c r="J15" s="192"/>
@@ -30312,10 +30393,12 @@
       <c r="B21" s="14" t="s">
         <v>131</v>
       </c>
-      <c r="C21" s="10"/>
+      <c r="C21" s="10">
+        <v>1</v>
+      </c>
       <c r="D21" s="48">
         <f t="shared" si="1"/>
-        <v>0</v>
+        <v>650</v>
       </c>
       <c r="F21" s="69" t="s">
         <v>99</v>
@@ -30581,7 +30664,7 @@
       <c r="C29" s="153"/>
       <c r="D29" s="157">
         <f>SUM(D6:D28)</f>
-        <v>0</v>
+        <v>351657</v>
       </c>
       <c r="F29" s="97" t="s">
         <v>55</v>
@@ -30589,7 +30672,7 @@
       <c r="G29" s="159"/>
       <c r="H29" s="119">
         <f>H15-H16-H17-H18-H19-H20-H22-H23-H24+H26+H27</f>
-        <v>0</v>
+        <v>318231</v>
       </c>
       <c r="I29" s="120"/>
       <c r="J29" s="121"/>
@@ -30822,10 +30905,12 @@
       <c r="B37" s="28" t="s">
         <v>66</v>
       </c>
-      <c r="C37" s="53"/>
+      <c r="C37" s="53">
+        <v>278</v>
+      </c>
       <c r="D37" s="12">
         <f>C37*111</f>
-        <v>0</v>
+        <v>30858</v>
       </c>
       <c r="F37" s="12">
         <v>100</v>
@@ -30856,10 +30941,12 @@
       <c r="B38" s="29" t="s">
         <v>68</v>
       </c>
-      <c r="C38" s="54"/>
+      <c r="C38" s="54">
+        <v>18</v>
+      </c>
       <c r="D38" s="12">
         <f>C38*84</f>
-        <v>0</v>
+        <v>1512</v>
       </c>
       <c r="F38" s="30">
         <v>50</v>
@@ -30890,10 +30977,12 @@
       <c r="B39" s="29" t="s">
         <v>70</v>
       </c>
-      <c r="C39" s="52"/>
+      <c r="C39" s="52">
+        <v>7</v>
+      </c>
       <c r="D39" s="31">
         <f>C39*4.5</f>
-        <v>0</v>
+        <v>31.5</v>
       </c>
       <c r="F39" s="12">
         <v>20</v>
@@ -30924,10 +31013,12 @@
       <c r="B40" s="27" t="s">
         <v>66</v>
       </c>
-      <c r="C40" s="63"/>
+      <c r="C40" s="63">
+        <v>4</v>
+      </c>
       <c r="D40" s="12">
         <f>C40*111</f>
-        <v>0</v>
+        <v>444</v>
       </c>
       <c r="F40" s="12">
         <v>10</v>
@@ -30987,10 +31078,12 @@
       <c r="B42" s="27" t="s">
         <v>70</v>
       </c>
-      <c r="C42" s="11"/>
+      <c r="C42" s="11">
+        <v>12</v>
+      </c>
       <c r="D42" s="12">
         <f>C42*2.25</f>
-        <v>0</v>
+        <v>27</v>
       </c>
       <c r="F42" s="39" t="s">
         <v>79</v>
@@ -31076,10 +31169,12 @@
       <c r="B45" s="27" t="s">
         <v>68</v>
       </c>
-      <c r="C45" s="33"/>
+      <c r="C45" s="33">
+        <v>2</v>
+      </c>
       <c r="D45" s="12">
         <f>C45*84</f>
-        <v>0</v>
+        <v>168</v>
       </c>
       <c r="F45" s="37"/>
       <c r="G45" s="62"/>
@@ -31133,10 +31228,12 @@
       <c r="B48" s="27" t="s">
         <v>66</v>
       </c>
-      <c r="C48" s="10"/>
+      <c r="C48" s="10">
+        <v>3</v>
+      </c>
       <c r="D48" s="12">
         <f>C48*78</f>
-        <v>0</v>
+        <v>234</v>
       </c>
       <c r="F48" s="59"/>
       <c r="G48" s="59"/>
@@ -31161,10 +31258,12 @@
       <c r="B49" s="29" t="s">
         <v>68</v>
       </c>
-      <c r="C49" s="33"/>
+      <c r="C49" s="33">
+        <v>1</v>
+      </c>
       <c r="D49" s="12">
         <f>C49*42</f>
-        <v>0</v>
+        <v>42</v>
       </c>
       <c r="F49" s="117" t="s">
         <v>86</v>
@@ -31195,10 +31294,12 @@
       <c r="B50" s="32" t="s">
         <v>70</v>
       </c>
-      <c r="C50" s="11"/>
+      <c r="C50" s="11">
+        <v>73</v>
+      </c>
       <c r="D50" s="12">
         <f>C50*1.5</f>
-        <v>0</v>
+        <v>109.5</v>
       </c>
       <c r="F50" s="118"/>
       <c r="G50" s="122"/>
@@ -31224,7 +31325,7 @@
       </c>
       <c r="G51" s="127">
         <f>G49-H29</f>
-        <v>0</v>
+        <v>-318231</v>
       </c>
       <c r="H51" s="128"/>
       <c r="I51" s="128"/>
@@ -31295,7 +31396,7 @@
       <c r="C54" s="99"/>
       <c r="D54" s="103">
         <f>SUM(D34:D53)</f>
-        <v>0</v>
+        <v>33426</v>
       </c>
       <c r="F54" s="21"/>
       <c r="J54" s="34"/>
